--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-19.xlsx
@@ -1522,7 +1522,7 @@
     <t>Atletico Grau</t>
   </si>
   <si>
-    <t>2026-09-17 01:25:34</t>
+    <t>2026-09-17 03:45:33</t>
   </si>
 </sst>
 </file>
@@ -2116,10 +2116,10 @@
         <v>336</v>
       </c>
       <c r="F2">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G2">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="H2">
         <v>3.1</v>
@@ -2131,7 +2131,7 @@
         <v>2.94</v>
       </c>
       <c r="K2">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="L2">
         <v>1.4</v>
@@ -2149,19 +2149,19 @@
         <v>1.68</v>
       </c>
       <c r="Q2">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="R2">
         <v>1.24</v>
       </c>
       <c r="S2">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="T2">
         <v>1.83</v>
       </c>
       <c r="U2">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="V2">
         <v>1.4</v>
@@ -2224,10 +2224,10 @@
         <v>1000</v>
       </c>
       <c r="AP2">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AQ2">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AR2">
         <v>1.48</v>
@@ -2242,19 +2242,19 @@
         <v>6</v>
       </c>
       <c r="AV2">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AW2">
         <v>1.48</v>
       </c>
       <c r="AX2">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AY2">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AZ2">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="BA2">
         <v>1.48</v>
@@ -2358,13 +2358,13 @@
         <v>337</v>
       </c>
       <c r="F3">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="G3">
         <v>1.8</v>
       </c>
       <c r="H3">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="I3">
         <v>6.2</v>
@@ -2382,19 +2382,19 @@
         <v>1.09</v>
       </c>
       <c r="N3">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="O3">
         <v>1.41</v>
       </c>
       <c r="P3">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="Q3">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R3">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="S3">
         <v>4.2</v>
@@ -2403,7 +2403,7 @@
         <v>2.1</v>
       </c>
       <c r="U3">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="V3">
         <v>1.19</v>
@@ -2415,7 +2415,7 @@
         <v>14</v>
       </c>
       <c r="Y3">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z3">
         <v>48</v>
@@ -2424,7 +2424,7 @@
         <v>190</v>
       </c>
       <c r="AB3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC3">
         <v>8.6</v>
@@ -2436,19 +2436,19 @@
         <v>100</v>
       </c>
       <c r="AF3">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG3">
         <v>11</v>
       </c>
       <c r="AH3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI3">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ3">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AK3">
         <v>22</v>
@@ -2457,16 +2457,16 @@
         <v>55</v>
       </c>
       <c r="AM3">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN3">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AO3">
         <v>150</v>
       </c>
       <c r="AP3">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ3">
         <v>14.5</v>
@@ -2478,16 +2478,16 @@
         <v>11.5</v>
       </c>
       <c r="AT3">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV3">
         <v>20</v>
       </c>
       <c r="AW3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AX3">
         <v>8.4</v>
@@ -2499,7 +2499,7 @@
         <v>21</v>
       </c>
       <c r="BA3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BB3">
         <v>15.5</v>
@@ -2517,7 +2517,7 @@
         <v>12.5</v>
       </c>
       <c r="BG3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -2600,22 +2600,22 @@
         <v>338</v>
       </c>
       <c r="F4">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G4">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="H4">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I4">
         <v>3.65</v>
       </c>
       <c r="J4">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K4">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L4">
         <v>1.34</v>
@@ -2624,34 +2624,34 @@
         <v>1.06</v>
       </c>
       <c r="N4">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="O4">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P4">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="Q4">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R4">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="S4">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T4">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U4">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="V4">
         <v>1.37</v>
       </c>
       <c r="W4">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="X4">
         <v>16</v>
@@ -2666,7 +2666,7 @@
         <v>80</v>
       </c>
       <c r="AB4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC4">
         <v>8.6</v>
@@ -2675,10 +2675,10 @@
         <v>15.5</v>
       </c>
       <c r="AE4">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AF4">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG4">
         <v>11.5</v>
@@ -2687,7 +2687,7 @@
         <v>17.5</v>
       </c>
       <c r="AI4">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AJ4">
         <v>29</v>
@@ -2702,37 +2702,37 @@
         <v>95</v>
       </c>
       <c r="AN4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AP4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS4">
         <v>10.5</v>
       </c>
       <c r="AT4">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU4">
         <v>7.4</v>
       </c>
       <c r="AV4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW4">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AX4">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY4">
         <v>10</v>
@@ -2744,19 +2744,19 @@
         <v>9.6</v>
       </c>
       <c r="BB4">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BC4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD4">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE4">
         <v>10.5</v>
       </c>
       <c r="BF4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BG4">
         <v>9.199999999999999</v>
@@ -2845,7 +2845,7 @@
         <v>1.23</v>
       </c>
       <c r="G5">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="H5">
         <v>8.6</v>
@@ -2881,7 +2881,7 @@
         <v>1.37</v>
       </c>
       <c r="S5">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="T5">
         <v>1.01</v>
@@ -3105,10 +3105,10 @@
         <v>1.01</v>
       </c>
       <c r="M6">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N6">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O6">
         <v>1.37</v>
@@ -3117,19 +3117,19 @@
         <v>1.73</v>
       </c>
       <c r="Q6">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R6">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="S6">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="T6">
         <v>1.78</v>
       </c>
       <c r="U6">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V6">
         <v>1.74</v>
@@ -3332,10 +3332,10 @@
         <v>5.1</v>
       </c>
       <c r="H7">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="I7">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="J7">
         <v>3.85</v>
@@ -3347,10 +3347,10 @@
         <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N7">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="O7">
         <v>1.26</v>
@@ -3359,13 +3359,13 @@
         <v>2.06</v>
       </c>
       <c r="Q7">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R7">
         <v>1.4</v>
       </c>
       <c r="S7">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="T7">
         <v>1.67</v>
@@ -3374,7 +3374,7 @@
         <v>2.06</v>
       </c>
       <c r="V7">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="W7">
         <v>1.24</v>
@@ -3485,7 +3485,7 @@
         <v>1.39</v>
       </c>
       <c r="BG7">
-        <v>8.6</v>
+        <v>1.28</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -3568,226 +3568,226 @@
         <v>342</v>
       </c>
       <c r="F8">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="H8">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="I8">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="J8">
         <v>3.1</v>
       </c>
       <c r="K8">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P8">
+        <v>1.62</v>
+      </c>
+      <c r="Q8">
+        <v>2.1</v>
+      </c>
+      <c r="R8">
+        <v>1.24</v>
+      </c>
+      <c r="S8">
+        <v>3.55</v>
+      </c>
+      <c r="T8">
+        <v>1.89</v>
+      </c>
+      <c r="U8">
+        <v>1.83</v>
+      </c>
+      <c r="V8">
+        <v>1.37</v>
+      </c>
+      <c r="W8">
         <v>1.56</v>
       </c>
-      <c r="Q8">
-        <v>2</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8">
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <v>0</v>
-      </c>
       <c r="X8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="s">
         <v>502</v>
@@ -4058,7 +4058,7 @@
         <v>4.2</v>
       </c>
       <c r="H10">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="I10">
         <v>2.32</v>
@@ -4067,7 +4067,7 @@
         <v>3.6</v>
       </c>
       <c r="K10">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -4778,22 +4778,22 @@
         <v>347</v>
       </c>
       <c r="F13">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="G13">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="H13">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I13">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J13">
         <v>3.2</v>
       </c>
       <c r="K13">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -5032,7 +5032,7 @@
         <v>2.6</v>
       </c>
       <c r="J14">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="K14">
         <v>4.2</v>
@@ -5262,19 +5262,19 @@
         <v>349</v>
       </c>
       <c r="F15">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G15">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="H15">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="I15">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="J15">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K15">
         <v>3.6</v>
@@ -5295,7 +5295,7 @@
         <v>1.75</v>
       </c>
       <c r="Q15">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -6260,7 +6260,7 @@
         <v>0</v>
       </c>
       <c r="P19">
-        <v>2.66</v>
+        <v>2.38</v>
       </c>
       <c r="Q19">
         <v>1.44</v>
@@ -6475,7 +6475,7 @@
         <v>1.12</v>
       </c>
       <c r="G20">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="H20">
         <v>1.35</v>
@@ -6717,7 +6717,7 @@
         <v>1.83</v>
       </c>
       <c r="G21">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="H21">
         <v>4</v>
@@ -6726,7 +6726,7 @@
         <v>4.4</v>
       </c>
       <c r="J21">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K21">
         <v>4.7</v>
@@ -6747,7 +6747,7 @@
         <v>2.62</v>
       </c>
       <c r="Q21">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -8411,7 +8411,7 @@
         <v>1.93</v>
       </c>
       <c r="G28">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H28">
         <v>3.35</v>
@@ -8420,7 +8420,7 @@
         <v>4</v>
       </c>
       <c r="J28">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="K28">
         <v>5.2</v>
@@ -8650,7 +8650,7 @@
         <v>363</v>
       </c>
       <c r="F29">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G29">
         <v>2.12</v>
@@ -8674,13 +8674,13 @@
         <v>1.06</v>
       </c>
       <c r="N29">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O29">
         <v>1.3</v>
       </c>
       <c r="P29">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q29">
         <v>1.91</v>
@@ -8695,7 +8695,7 @@
         <v>1.76</v>
       </c>
       <c r="U29">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V29">
         <v>0</v>
@@ -8707,10 +8707,10 @@
         <v>15</v>
       </c>
       <c r="Y29">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z29">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AA29">
         <v>80</v>
@@ -8740,7 +8740,7 @@
         <v>55</v>
       </c>
       <c r="AJ29">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK29">
         <v>21</v>
@@ -8779,10 +8779,10 @@
         <v>14.5</v>
       </c>
       <c r="AW29">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AX29">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY29">
         <v>9.800000000000001</v>
@@ -8800,7 +8800,7 @@
         <v>19.5</v>
       </c>
       <c r="BD29">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BE29">
         <v>55</v>
@@ -8913,7 +8913,7 @@
         <v>0</v>
       </c>
       <c r="M30">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N30">
         <v>0</v>
@@ -8922,7 +8922,7 @@
         <v>0</v>
       </c>
       <c r="P30">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="Q30">
         <v>1.68</v>
@@ -9376,19 +9376,19 @@
         <v>366</v>
       </c>
       <c r="F32">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="G32">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="H32">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="I32">
         <v>3.05</v>
       </c>
       <c r="J32">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K32">
         <v>3.65</v>
@@ -9406,7 +9406,7 @@
         <v>0</v>
       </c>
       <c r="P32">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q32">
         <v>1.91</v>
@@ -9621,7 +9621,7 @@
         <v>2.36</v>
       </c>
       <c r="G33">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="H33">
         <v>2.74</v>
@@ -9630,7 +9630,7 @@
         <v>3.05</v>
       </c>
       <c r="J33">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="K33">
         <v>4.1</v>
@@ -9651,7 +9651,7 @@
         <v>1.88</v>
       </c>
       <c r="Q33">
-        <v>1.02</v>
+        <v>1.92</v>
       </c>
       <c r="R33">
         <v>0</v>
@@ -9890,10 +9890,10 @@
         <v>0</v>
       </c>
       <c r="P34">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="Q34">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R34">
         <v>0</v>
@@ -10344,10 +10344,10 @@
         <v>370</v>
       </c>
       <c r="F36">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G36">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H36">
         <v>3.2</v>
@@ -11318,16 +11318,16 @@
         <v>2.32</v>
       </c>
       <c r="H40">
-        <v>2.92</v>
+        <v>2.68</v>
       </c>
       <c r="I40">
         <v>3.85</v>
       </c>
       <c r="J40">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="K40">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -11829,7 +11829,7 @@
         <v>2.22</v>
       </c>
       <c r="Q42">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R42">
         <v>0</v>
@@ -12289,7 +12289,7 @@
         <v>3.35</v>
       </c>
       <c r="I44">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="J44">
         <v>3.6</v>
@@ -12791,10 +12791,10 @@
         <v>3.5</v>
       </c>
       <c r="O46">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P46">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -12848,7 +12848,7 @@
         <v>11</v>
       </c>
       <c r="AH46">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI46">
         <v>70</v>
@@ -12884,7 +12884,7 @@
         <v>36</v>
       </c>
       <c r="AT46">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU46">
         <v>7.4</v>
@@ -13015,7 +13015,7 @@
         <v>2.48</v>
       </c>
       <c r="I47">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="J47">
         <v>3.4</v>
@@ -13251,7 +13251,7 @@
         <v>1.61</v>
       </c>
       <c r="G48">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="H48">
         <v>4.9</v>
@@ -13263,7 +13263,7 @@
         <v>3.95</v>
       </c>
       <c r="K48">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -13502,7 +13502,7 @@
         <v>5.1</v>
       </c>
       <c r="J49">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K49">
         <v>3.8</v>
@@ -13523,7 +13523,7 @@
         <v>1.8</v>
       </c>
       <c r="Q49">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R49">
         <v>0</v>
@@ -14605,7 +14605,7 @@
         <v>22</v>
       </c>
       <c r="BC53">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BD53">
         <v>17.5</v>
@@ -14700,7 +14700,7 @@
         <v>388</v>
       </c>
       <c r="F54">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G54">
         <v>3.1</v>
@@ -14724,7 +14724,7 @@
         <v>1.04</v>
       </c>
       <c r="N54">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O54">
         <v>1.19</v>
@@ -14739,7 +14739,7 @@
         <v>1.64</v>
       </c>
       <c r="S54">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="T54">
         <v>1.53</v>
@@ -14760,7 +14760,7 @@
         <v>15.5</v>
       </c>
       <c r="Z54">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AA54">
         <v>32</v>
@@ -14796,7 +14796,7 @@
         <v>29</v>
       </c>
       <c r="AL54">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM54">
         <v>55</v>
@@ -14820,7 +14820,7 @@
         <v>21</v>
       </c>
       <c r="AT54">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AU54">
         <v>8.6</v>
@@ -14942,7 +14942,7 @@
         <v>389</v>
       </c>
       <c r="F55">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="G55">
         <v>6.4</v>
@@ -14957,7 +14957,7 @@
         <v>3.7</v>
       </c>
       <c r="K55">
-        <v>100</v>
+        <v>4.1</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -15190,7 +15190,7 @@
         <v>2.44</v>
       </c>
       <c r="H56">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="I56">
         <v>2.92</v>
@@ -15214,16 +15214,16 @@
         <v>1.15</v>
       </c>
       <c r="P56">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q56">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="R56">
         <v>1.86</v>
       </c>
       <c r="S56">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="T56">
         <v>1.43</v>
@@ -15334,7 +15334,7 @@
         <v>18.5</v>
       </c>
       <c r="BD56">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE56">
         <v>32</v>
@@ -15674,7 +15674,7 @@
         <v>2.9</v>
       </c>
       <c r="H58">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="I58">
         <v>2.58</v>
@@ -15704,10 +15704,10 @@
         <v>1.63</v>
       </c>
       <c r="R58">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S58">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="T58">
         <v>1.56</v>
@@ -15916,7 +15916,7 @@
         <v>3.55</v>
       </c>
       <c r="H59">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="I59">
         <v>2.42</v>
@@ -16158,13 +16158,13 @@
         <v>1.93</v>
       </c>
       <c r="H60">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I60">
         <v>4.8</v>
       </c>
       <c r="J60">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K60">
         <v>4</v>
@@ -16651,7 +16651,7 @@
         <v>3.8</v>
       </c>
       <c r="K62">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -17120,22 +17120,22 @@
         <v>398</v>
       </c>
       <c r="F64">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="G64">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="H64">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="I64">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="J64">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="K64">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="L64">
         <v>0</v>
@@ -17153,7 +17153,7 @@
         <v>2</v>
       </c>
       <c r="Q64">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="R64">
         <v>0</v>
@@ -17604,10 +17604,10 @@
         <v>400</v>
       </c>
       <c r="F66">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="G66">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="H66">
         <v>1.55</v>
@@ -17634,7 +17634,7 @@
         <v>0</v>
       </c>
       <c r="P66">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="Q66">
         <v>1.49</v>
@@ -17876,7 +17876,7 @@
         <v>0</v>
       </c>
       <c r="P67">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q67">
         <v>1.67</v>
@@ -18088,7 +18088,7 @@
         <v>402</v>
       </c>
       <c r="F68">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="G68">
         <v>2.2</v>
@@ -18103,7 +18103,7 @@
         <v>3.5</v>
       </c>
       <c r="K68">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L68">
         <v>0</v>
@@ -18575,10 +18575,10 @@
         <v>4.6</v>
       </c>
       <c r="G70">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="H70">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="I70">
         <v>1.82</v>
@@ -18587,7 +18587,7 @@
         <v>3.9</v>
       </c>
       <c r="K70">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L70">
         <v>0</v>
@@ -18602,10 +18602,10 @@
         <v>0</v>
       </c>
       <c r="P70">
-        <v>1.25</v>
+        <v>2.14</v>
       </c>
       <c r="Q70">
-        <v>1.8</v>
+        <v>1.04</v>
       </c>
       <c r="R70">
         <v>0</v>
@@ -19313,7 +19313,7 @@
         <v>3.35</v>
       </c>
       <c r="K73">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="L73">
         <v>0</v>
@@ -19328,10 +19328,10 @@
         <v>0</v>
       </c>
       <c r="P73">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q73">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="R73">
         <v>0</v>
@@ -19540,7 +19540,7 @@
         <v>408</v>
       </c>
       <c r="F74">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G74">
         <v>2.46</v>
@@ -19549,10 +19549,10 @@
         <v>3.5</v>
       </c>
       <c r="I74">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="J74">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="K74">
         <v>3.8</v>
@@ -19570,7 +19570,7 @@
         <v>0</v>
       </c>
       <c r="P74">
-        <v>1.12</v>
+        <v>1.72</v>
       </c>
       <c r="Q74">
         <v>1.01</v>
@@ -20266,16 +20266,16 @@
         <v>411</v>
       </c>
       <c r="F77">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="G77">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="H77">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I77">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="J77">
         <v>3.2</v>
@@ -20296,10 +20296,10 @@
         <v>0</v>
       </c>
       <c r="P77">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="Q77">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="R77">
         <v>0</v>
@@ -20992,7 +20992,7 @@
         <v>414</v>
       </c>
       <c r="F80">
-        <v>1.42</v>
+        <v>2.36</v>
       </c>
       <c r="G80">
         <v>2.78</v>
@@ -21007,7 +21007,7 @@
         <v>2.78</v>
       </c>
       <c r="K80">
-        <v>950</v>
+        <v>4.5</v>
       </c>
       <c r="L80">
         <v>0</v>
@@ -21476,7 +21476,7 @@
         <v>416</v>
       </c>
       <c r="F82">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="G82">
         <v>2.82</v>
@@ -21491,7 +21491,7 @@
         <v>3.6</v>
       </c>
       <c r="K82">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L82">
         <v>0</v>
@@ -21718,7 +21718,7 @@
         <v>417</v>
       </c>
       <c r="F83">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="G83">
         <v>2.16</v>
@@ -21727,13 +21727,13 @@
         <v>3.5</v>
       </c>
       <c r="I83">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="J83">
         <v>3.85</v>
       </c>
       <c r="K83">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="L83">
         <v>0</v>
@@ -22456,7 +22456,7 @@
         <v>1.69</v>
       </c>
       <c r="J86">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="K86">
         <v>4.8</v>
@@ -22474,7 +22474,7 @@
         <v>0</v>
       </c>
       <c r="P86">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="Q86">
         <v>1.72</v>
@@ -22937,10 +22937,10 @@
         <v>5.3</v>
       </c>
       <c r="I88">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J88">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K88">
         <v>4.7</v>
@@ -22982,7 +22982,7 @@
         <v>0</v>
       </c>
       <c r="X88">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y88">
         <v>22</v>
@@ -23009,7 +23009,7 @@
         <v>11</v>
       </c>
       <c r="AG88">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH88">
         <v>19.5</v>
@@ -23042,7 +23042,7 @@
         <v>20</v>
       </c>
       <c r="AR88">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AS88">
         <v>44</v>
@@ -23087,7 +23087,7 @@
         <v>6.8</v>
       </c>
       <c r="BG88">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BH88">
         <v>1000</v>
@@ -23173,16 +23173,16 @@
         <v>5.1</v>
       </c>
       <c r="G89">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="H89">
         <v>1.75</v>
       </c>
       <c r="I89">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="J89">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K89">
         <v>4.3</v>
@@ -23191,7 +23191,7 @@
         <v>0</v>
       </c>
       <c r="M89">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N89">
         <v>4.4</v>
@@ -23236,7 +23236,7 @@
         <v>18</v>
       </c>
       <c r="AB89">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AC89">
         <v>8.800000000000001</v>
@@ -23275,7 +23275,7 @@
         <v>70</v>
       </c>
       <c r="AO89">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP89">
         <v>16.5</v>
@@ -23314,7 +23314,7 @@
         <v>29</v>
       </c>
       <c r="BB89">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="BC89">
         <v>50</v>
@@ -23329,7 +23329,7 @@
         <v>60</v>
       </c>
       <c r="BG89">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BH89">
         <v>970</v>
@@ -23442,10 +23442,10 @@
         <v>0</v>
       </c>
       <c r="P90">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
       <c r="Q90">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R90">
         <v>0</v>
@@ -23675,7 +23675,7 @@
         <v>0</v>
       </c>
       <c r="M91">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N91">
         <v>0</v>
@@ -23684,7 +23684,7 @@
         <v>0</v>
       </c>
       <c r="P91">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q91">
         <v>1.91</v>
@@ -23896,22 +23896,22 @@
         <v>426</v>
       </c>
       <c r="F92">
+        <v>2.16</v>
+      </c>
+      <c r="G92">
         <v>2.18</v>
       </c>
-      <c r="G92">
-        <v>2.22</v>
-      </c>
       <c r="H92">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="I92">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J92">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K92">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L92">
         <v>0</v>
@@ -23926,7 +23926,7 @@
         <v>0</v>
       </c>
       <c r="P92">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="Q92">
         <v>2.1</v>
@@ -24138,19 +24138,19 @@
         <v>427</v>
       </c>
       <c r="F93">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G93">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="H93">
         <v>5</v>
       </c>
       <c r="I93">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J93">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K93">
         <v>4.3</v>
@@ -24168,10 +24168,10 @@
         <v>0</v>
       </c>
       <c r="P93">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="Q93">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="R93">
         <v>0</v>
@@ -24383,10 +24383,10 @@
         <v>3.1</v>
       </c>
       <c r="G94">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H94">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="I94">
         <v>2.42</v>
@@ -24413,7 +24413,7 @@
         <v>2.12</v>
       </c>
       <c r="Q94">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="R94">
         <v>0</v>
@@ -24622,7 +24622,7 @@
         <v>429</v>
       </c>
       <c r="F95">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="G95">
         <v>3.05</v>
@@ -24631,7 +24631,7 @@
         <v>2.52</v>
       </c>
       <c r="I95">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="J95">
         <v>3.55</v>
@@ -24885,7 +24885,7 @@
         <v>0</v>
       </c>
       <c r="M96">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N96">
         <v>4.5</v>
@@ -24894,7 +24894,7 @@
         <v>1.26</v>
       </c>
       <c r="P96">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q96">
         <v>1.8</v>
@@ -24906,7 +24906,7 @@
         <v>3</v>
       </c>
       <c r="T96">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U96">
         <v>2.24</v>
@@ -24939,7 +24939,7 @@
         <v>18.5</v>
       </c>
       <c r="AE96">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="AF96">
         <v>12</v>
@@ -24969,7 +24969,7 @@
         <v>10</v>
       </c>
       <c r="AO96">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="AP96">
         <v>16.5</v>
@@ -24978,7 +24978,7 @@
         <v>17</v>
       </c>
       <c r="AR96">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS96">
         <v>50</v>
@@ -25002,10 +25002,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ96">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA96">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BB96">
         <v>17.5</v>
@@ -25017,13 +25017,13 @@
         <v>28</v>
       </c>
       <c r="BE96">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BF96">
         <v>9.199999999999999</v>
       </c>
       <c r="BG96">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="BH96">
         <v>4.2</v>
@@ -25106,10 +25106,10 @@
         <v>431</v>
       </c>
       <c r="F97">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="G97">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="H97">
         <v>5.8</v>
@@ -25118,7 +25118,7 @@
         <v>6.4</v>
       </c>
       <c r="J97">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="K97">
         <v>4.2</v>
@@ -25127,31 +25127,31 @@
         <v>0</v>
       </c>
       <c r="M97">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N97">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="O97">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="P97">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="Q97">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="R97">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S97">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="T97">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U97">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="V97">
         <v>0</v>
@@ -25160,10 +25160,10 @@
         <v>0</v>
       </c>
       <c r="X97">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y97">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="Z97">
         <v>50</v>
@@ -25172,7 +25172,7 @@
         <v>190</v>
       </c>
       <c r="AB97">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC97">
         <v>9.199999999999999</v>
@@ -25199,37 +25199,37 @@
         <v>16.5</v>
       </c>
       <c r="AK97">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL97">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM97">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN97">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AO97">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AP97">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ97">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR97">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS97">
         <v>44</v>
       </c>
       <c r="AT97">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AU97">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV97">
         <v>20</v>
@@ -25238,22 +25238,22 @@
         <v>36</v>
       </c>
       <c r="AX97">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY97">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ97">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BA97">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BB97">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC97">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD97">
         <v>32</v>
@@ -25262,7 +25262,7 @@
         <v>44</v>
       </c>
       <c r="BF97">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BG97">
         <v>40</v>
@@ -25277,7 +25277,7 @@
         <v>1000</v>
       </c>
       <c r="BK97">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="BL97">
         <v>1000</v>
@@ -25295,7 +25295,7 @@
         <v>1000</v>
       </c>
       <c r="BQ97">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="BR97">
         <v>1000</v>
@@ -25348,22 +25348,22 @@
         <v>432</v>
       </c>
       <c r="F98">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="G98">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="H98">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="I98">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="J98">
         <v>4.2</v>
       </c>
       <c r="K98">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="L98">
         <v>0</v>
@@ -25378,10 +25378,10 @@
         <v>0</v>
       </c>
       <c r="P98">
-        <v>1.12</v>
+        <v>2.62</v>
       </c>
       <c r="Q98">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="R98">
         <v>0</v>
@@ -25838,7 +25838,7 @@
         <v>1.73</v>
       </c>
       <c r="H100">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="I100">
         <v>8</v>
@@ -26316,7 +26316,7 @@
         <v>436</v>
       </c>
       <c r="F102">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="G102">
         <v>3.35</v>
@@ -26325,13 +26325,13 @@
         <v>2.36</v>
       </c>
       <c r="I102">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="J102">
         <v>3.65</v>
       </c>
       <c r="K102">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L102">
         <v>0</v>
@@ -26803,13 +26803,13 @@
         <v>2.94</v>
       </c>
       <c r="G104">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="H104">
         <v>2.14</v>
       </c>
       <c r="I104">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="J104">
         <v>4</v>
@@ -27559,7 +27559,7 @@
         <v>2.14</v>
       </c>
       <c r="Q107">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="R107">
         <v>0</v>
@@ -28264,7 +28264,7 @@
         <v>3.95</v>
       </c>
       <c r="J110">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K110">
         <v>4</v>
@@ -28291,7 +28291,7 @@
         <v>1.54</v>
       </c>
       <c r="S110">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="T110">
         <v>1.61</v>
@@ -28315,7 +28315,7 @@
         <v>36</v>
       </c>
       <c r="AA110">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AB110">
         <v>12.5</v>
@@ -28363,7 +28363,7 @@
         <v>18</v>
       </c>
       <c r="AQ110">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AR110">
         <v>8.800000000000001</v>
@@ -28381,7 +28381,7 @@
         <v>14</v>
       </c>
       <c r="AW110">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX110">
         <v>13.5</v>
@@ -28405,7 +28405,7 @@
         <v>22</v>
       </c>
       <c r="BE110">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF110">
         <v>9.800000000000001</v>
@@ -28429,13 +28429,13 @@
         <v>100</v>
       </c>
       <c r="BM110">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BN110">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BO110">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP110">
         <v>16.5</v>
@@ -28447,7 +28447,7 @@
         <v>28</v>
       </c>
       <c r="BS110">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT110">
         <v>7.2</v>
@@ -28459,13 +28459,13 @@
         <v>32</v>
       </c>
       <c r="BW110">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX110">
         <v>40</v>
       </c>
       <c r="BY110">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BZ110">
         <v>0</v>
@@ -28500,7 +28500,7 @@
         <v>2.66</v>
       </c>
       <c r="H111">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="I111">
         <v>3.65</v>
@@ -28978,13 +28978,13 @@
         <v>447</v>
       </c>
       <c r="F113">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G113">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="H113">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I113">
         <v>5.6</v>
@@ -28993,7 +28993,7 @@
         <v>3.6</v>
       </c>
       <c r="K113">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L113">
         <v>0</v>
@@ -29020,10 +29020,10 @@
         <v>0</v>
       </c>
       <c r="T113">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U113">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V113">
         <v>0</v>
@@ -29035,10 +29035,10 @@
         <v>12.5</v>
       </c>
       <c r="Y113">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z113">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AA113">
         <v>170</v>
@@ -29062,7 +29062,7 @@
         <v>11</v>
       </c>
       <c r="AH113">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI113">
         <v>110</v>
@@ -29092,10 +29092,10 @@
         <v>12.5</v>
       </c>
       <c r="AR113">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AS113">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AT113">
         <v>6.2</v>
@@ -29107,37 +29107,37 @@
         <v>16.5</v>
       </c>
       <c r="AW113">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AX113">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY113">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ113">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BA113">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB113">
         <v>16.5</v>
       </c>
       <c r="BC113">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BD113">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="BE113">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BF113">
         <v>14</v>
       </c>
       <c r="BG113">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BH113">
         <v>0</v>
@@ -29952,7 +29952,7 @@
         <v>2.84</v>
       </c>
       <c r="H117">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="I117">
         <v>2.72</v>
@@ -29985,7 +29985,7 @@
         <v>1.57</v>
       </c>
       <c r="S117">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="T117">
         <v>1.55</v>
@@ -30188,10 +30188,10 @@
         <v>452</v>
       </c>
       <c r="F118">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="G118">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="H118">
         <v>7.4</v>
@@ -30203,7 +30203,7 @@
         <v>6.4</v>
       </c>
       <c r="K118">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="L118">
         <v>0</v>
@@ -30436,7 +30436,7 @@
         <v>1.89</v>
       </c>
       <c r="H119">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I119">
         <v>6.4</v>
@@ -30445,7 +30445,7 @@
         <v>4.1</v>
       </c>
       <c r="K119">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="L119">
         <v>0</v>
@@ -30672,16 +30672,16 @@
         <v>454</v>
       </c>
       <c r="F120">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="G120">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="H120">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I120">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J120">
         <v>4.1</v>
@@ -30702,7 +30702,7 @@
         <v>1.23</v>
       </c>
       <c r="P120">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q120">
         <v>1.7</v>
@@ -30729,10 +30729,10 @@
         <v>21</v>
       </c>
       <c r="Y120">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Z120">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AA120">
         <v>1000</v>
@@ -30762,7 +30762,7 @@
         <v>160</v>
       </c>
       <c r="AJ120">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK120">
         <v>19</v>
@@ -30816,7 +30816,7 @@
         <v>26</v>
       </c>
       <c r="BB120">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC120">
         <v>16</v>
@@ -30831,7 +30831,7 @@
         <v>8.6</v>
       </c>
       <c r="BG120">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="BH120">
         <v>970</v>
@@ -30914,22 +30914,22 @@
         <v>455</v>
       </c>
       <c r="F121">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="G121">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="H121">
-        <v>1.27</v>
+        <v>5.3</v>
       </c>
       <c r="I121">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="J121">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="K121">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="L121">
         <v>0</v>
@@ -30944,7 +30944,7 @@
         <v>0</v>
       </c>
       <c r="P121">
-        <v>2.04</v>
+        <v>1.07</v>
       </c>
       <c r="Q121">
         <v>1.76</v>
@@ -31156,16 +31156,16 @@
         <v>456</v>
       </c>
       <c r="F122">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="G122">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="H122">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="I122">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="J122">
         <v>3.2</v>
@@ -31413,7 +31413,7 @@
         <v>3.35</v>
       </c>
       <c r="K123">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="L123">
         <v>0</v>
@@ -31670,7 +31670,7 @@
         <v>1.14</v>
       </c>
       <c r="P124">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="Q124">
         <v>1.43</v>
@@ -31679,7 +31679,7 @@
         <v>1.91</v>
       </c>
       <c r="S124">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="T124">
         <v>1.41</v>
@@ -31697,7 +31697,7 @@
         <v>34</v>
       </c>
       <c r="Y124">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z124">
         <v>29</v>
@@ -31763,13 +31763,13 @@
         <v>18</v>
       </c>
       <c r="AU124">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV124">
         <v>12.5</v>
       </c>
       <c r="AW124">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AX124">
         <v>21</v>
@@ -31781,7 +31781,7 @@
         <v>11.5</v>
       </c>
       <c r="BA124">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="BB124">
         <v>23</v>
@@ -31793,7 +31793,7 @@
         <v>21</v>
       </c>
       <c r="BE124">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BF124">
         <v>8.800000000000001</v>
@@ -31891,7 +31891,7 @@
         <v>5.7</v>
       </c>
       <c r="I125">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J125">
         <v>4.2</v>
@@ -31912,7 +31912,7 @@
         <v>1.28</v>
       </c>
       <c r="P125">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q125">
         <v>1.84</v>
@@ -31936,7 +31936,7 @@
         <v>0</v>
       </c>
       <c r="X125">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y125">
         <v>21</v>
@@ -31993,10 +31993,10 @@
         <v>15.5</v>
       </c>
       <c r="AQ125">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AR125">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="AS125">
         <v>42</v>
@@ -32850,7 +32850,7 @@
         <v>463</v>
       </c>
       <c r="F129">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="G129">
         <v>3.3</v>
@@ -32859,7 +32859,7 @@
         <v>2.2</v>
       </c>
       <c r="I129">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="J129">
         <v>4</v>
@@ -32880,7 +32880,7 @@
         <v>0</v>
       </c>
       <c r="P129">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="Q129">
         <v>1.5</v>
@@ -32895,7 +32895,7 @@
         <v>1.47</v>
       </c>
       <c r="U129">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="V129">
         <v>0</v>
@@ -32952,13 +32952,13 @@
         <v>55</v>
       </c>
       <c r="AN129">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AO129">
-        <v>42</v>
+        <v>9.6</v>
       </c>
       <c r="AP129">
-        <v>4.6</v>
+        <v>7.6</v>
       </c>
       <c r="AQ129">
         <v>15</v>
@@ -32967,13 +32967,13 @@
         <v>17</v>
       </c>
       <c r="AS129">
-        <v>4.6</v>
+        <v>7.6</v>
       </c>
       <c r="AT129">
         <v>19</v>
       </c>
       <c r="AU129">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV129">
         <v>10.5</v>
@@ -32982,7 +32982,7 @@
         <v>17.5</v>
       </c>
       <c r="AX129">
-        <v>4.6</v>
+        <v>7.6</v>
       </c>
       <c r="AY129">
         <v>13</v>
@@ -32994,22 +32994,22 @@
         <v>21</v>
       </c>
       <c r="BB129">
-        <v>4.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC129">
-        <v>4.6</v>
+        <v>7.6</v>
       </c>
       <c r="BD129">
         <v>21</v>
       </c>
       <c r="BE129">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="BF129">
         <v>14</v>
       </c>
       <c r="BG129">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH129">
         <v>0</v>
@@ -33098,16 +33098,16 @@
         <v>1.62</v>
       </c>
       <c r="H130">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="I130">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J130">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="K130">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="L130">
         <v>0</v>
@@ -33340,16 +33340,16 @@
         <v>2.36</v>
       </c>
       <c r="H131">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="I131">
         <v>5.4</v>
       </c>
       <c r="J131">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K131">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="L131">
         <v>0</v>
@@ -34547,7 +34547,7 @@
         <v>5.9</v>
       </c>
       <c r="G136">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="H136">
         <v>1.53</v>
@@ -34556,7 +34556,7 @@
         <v>1.61</v>
       </c>
       <c r="J136">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K136">
         <v>5</v>
@@ -35031,7 +35031,7 @@
         <v>1.48</v>
       </c>
       <c r="G138">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="H138">
         <v>6.2</v>
@@ -35545,7 +35545,7 @@
         <v>1.64</v>
       </c>
       <c r="Q140">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="R140">
         <v>0</v>
@@ -35754,19 +35754,19 @@
         <v>475</v>
       </c>
       <c r="F141">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="G141">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="H141">
         <v>2.66</v>
       </c>
       <c r="I141">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="J141">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K141">
         <v>4.4</v>
@@ -36492,7 +36492,7 @@
         <v>4.8</v>
       </c>
       <c r="J144">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K144">
         <v>4.4</v>
@@ -36510,10 +36510,10 @@
         <v>0</v>
       </c>
       <c r="P144">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="Q144">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="R144">
         <v>0</v>
@@ -37690,22 +37690,22 @@
         <v>483</v>
       </c>
       <c r="F149">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="G149">
         <v>1.34</v>
       </c>
       <c r="H149">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="I149">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="J149">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="K149">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="L149">
         <v>0</v>
@@ -37723,7 +37723,7 @@
         <v>3.85</v>
       </c>
       <c r="Q149">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="R149">
         <v>0</v>
@@ -37932,10 +37932,10 @@
         <v>484</v>
       </c>
       <c r="F150">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="G150">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="H150">
         <v>2.06</v>
@@ -37944,10 +37944,10 @@
         <v>2.24</v>
       </c>
       <c r="J150">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="K150">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="L150">
         <v>0</v>
@@ -38174,16 +38174,16 @@
         <v>485</v>
       </c>
       <c r="F151">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="G151">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="H151">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="I151">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J151">
         <v>4.1</v>
@@ -38204,7 +38204,7 @@
         <v>0</v>
       </c>
       <c r="P151">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="Q151">
         <v>1.47</v>
@@ -38231,7 +38231,7 @@
         <v>34</v>
       </c>
       <c r="Y151">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z151">
         <v>24</v>
@@ -38288,7 +38288,7 @@
         <v>16.5</v>
       </c>
       <c r="AR151">
-        <v>6</v>
+        <v>17.5</v>
       </c>
       <c r="AS151">
         <v>6.8</v>
@@ -38300,7 +38300,7 @@
         <v>10</v>
       </c>
       <c r="AV151">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW151">
         <v>6.2</v>
@@ -38446,10 +38446,10 @@
         <v>1.28</v>
       </c>
       <c r="P152">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q152">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="R152">
         <v>1.45</v>
@@ -38557,7 +38557,7 @@
         <v>15</v>
       </c>
       <c r="BA152">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB152">
         <v>34</v>
@@ -38569,10 +38569,10 @@
         <v>27</v>
       </c>
       <c r="BE152">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BF152">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BG152">
         <v>11.5</v>
@@ -38673,7 +38673,7 @@
         <v>5</v>
       </c>
       <c r="K153">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="L153">
         <v>0</v>
@@ -38688,10 +38688,10 @@
         <v>0</v>
       </c>
       <c r="P153">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q153">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="R153">
         <v>0</v>
@@ -38933,7 +38933,7 @@
         <v>2.64</v>
       </c>
       <c r="Q154">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R154">
         <v>1.66</v>
@@ -38942,7 +38942,7 @@
         <v>2.4</v>
       </c>
       <c r="T154">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="U154">
         <v>2.76</v>
@@ -38996,10 +38996,10 @@
         <v>24</v>
       </c>
       <c r="AL154">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AM154">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AN154">
         <v>10.5</v>
@@ -39008,16 +39008,16 @@
         <v>26</v>
       </c>
       <c r="AP154">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AQ154">
         <v>17.5</v>
       </c>
       <c r="AR154">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS154">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT154">
         <v>13.5</v>
@@ -39029,7 +39029,7 @@
         <v>13</v>
       </c>
       <c r="AW154">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AX154">
         <v>16</v>
@@ -39041,10 +39041,10 @@
         <v>12.5</v>
       </c>
       <c r="BA154">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BB154">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BC154">
         <v>17.5</v>
@@ -39053,7 +39053,7 @@
         <v>19</v>
       </c>
       <c r="BE154">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF154">
         <v>9.4</v>
@@ -39172,7 +39172,7 @@
         <v>1.36</v>
       </c>
       <c r="P155">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="Q155">
         <v>2.08</v>
@@ -39417,7 +39417,7 @@
         <v>1.98</v>
       </c>
       <c r="Q156">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="R156">
         <v>1.38</v>
@@ -39456,7 +39456,7 @@
         <v>9</v>
       </c>
       <c r="AD156">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AE156">
         <v>70</v>
@@ -39468,7 +39468,7 @@
         <v>10.5</v>
       </c>
       <c r="AH156">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI156">
         <v>70</v>
@@ -39477,7 +39477,7 @@
         <v>22</v>
       </c>
       <c r="AK156">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AL156">
         <v>38</v>
@@ -39498,7 +39498,7 @@
         <v>15.5</v>
       </c>
       <c r="AR156">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AS156">
         <v>9.800000000000001</v>
@@ -39513,7 +39513,7 @@
         <v>17</v>
       </c>
       <c r="AW156">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AX156">
         <v>9.800000000000001</v>
@@ -39525,7 +39525,7 @@
         <v>17.5</v>
       </c>
       <c r="BA156">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BB156">
         <v>16.5</v>
@@ -39534,7 +39534,7 @@
         <v>16.5</v>
       </c>
       <c r="BD156">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BE156">
         <v>9.800000000000001</v>
@@ -39874,7 +39874,7 @@
         <v>1000</v>
       </c>
       <c r="H158">
-        <v>1.34</v>
+        <v>1.12</v>
       </c>
       <c r="I158">
         <v>1000</v>
@@ -40134,22 +40134,22 @@
         <v>1.06</v>
       </c>
       <c r="N159">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O159">
         <v>1.27</v>
       </c>
       <c r="P159">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="Q159">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="R159">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S159">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="T159">
         <v>1.68</v>
@@ -40251,7 +40251,7 @@
         <v>14</v>
       </c>
       <c r="BA159">
-        <v>8.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="BB159">
         <v>32</v>
@@ -40266,7 +40266,7 @@
         <v>9</v>
       </c>
       <c r="BF159">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BG159">
         <v>17.5</v>
@@ -40594,7 +40594,7 @@
         <v>495</v>
       </c>
       <c r="F161">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="G161">
         <v>2.74</v>
@@ -40609,7 +40609,7 @@
         <v>3.85</v>
       </c>
       <c r="K161">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L161">
         <v>0</v>
@@ -40624,10 +40624,10 @@
         <v>0</v>
       </c>
       <c r="P161">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="Q161">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="R161">
         <v>0</v>
@@ -41078,13 +41078,13 @@
         <v>497</v>
       </c>
       <c r="F163">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="G163">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="H163">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="I163">
         <v>1.22</v>
@@ -41093,7 +41093,7 @@
         <v>8.4</v>
       </c>
       <c r="K163">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L163">
         <v>0</v>
@@ -41114,13 +41114,13 @@
         <v>1.29</v>
       </c>
       <c r="R163">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="S163">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="T163">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U163">
         <v>2.4</v>
@@ -41147,7 +41147,7 @@
         <v>100</v>
       </c>
       <c r="AC163">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AD163">
         <v>13.5</v>
@@ -41195,7 +41195,7 @@
         <v>10.5</v>
       </c>
       <c r="AS163">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AT163">
         <v>34</v>
@@ -41216,13 +41216,13 @@
         <v>29</v>
       </c>
       <c r="AZ163">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BA163">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BB163">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BC163">
         <v>48</v>
@@ -41231,7 +41231,7 @@
         <v>42</v>
       </c>
       <c r="BE163">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="BF163">
         <v>46</v>
@@ -41240,64 +41240,64 @@
         <v>2.54</v>
       </c>
       <c r="BH163">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BI163">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BJ163">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK163">
         <v>1.01</v>
       </c>
       <c r="BL163">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM163">
         <v>1.01</v>
       </c>
       <c r="BN163">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BO163">
         <v>1.01</v>
       </c>
       <c r="BP163">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BQ163">
         <v>1.01</v>
       </c>
       <c r="BR163">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BS163">
         <v>1.01</v>
       </c>
       <c r="BT163">
-        <v>970</v>
+        <v>5.2</v>
       </c>
       <c r="BU163">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BV163">
-        <v>970</v>
+        <v>7.8</v>
       </c>
       <c r="BW163">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BX163">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BY163">
         <v>1.01</v>
       </c>
       <c r="BZ163">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="CA163">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="CB163" t="s">
         <v>502</v>
@@ -41320,7 +41320,7 @@
         <v>498</v>
       </c>
       <c r="F164">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="G164">
         <v>4.3</v>
@@ -41353,7 +41353,7 @@
         <v>1.07</v>
       </c>
       <c r="Q164">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="R164">
         <v>0</v>
